--- a/bot/data/users.xlsx
+++ b/bot/data/users.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" customFormat="1" s="1">
@@ -436,50 +436,20 @@
           <t>user_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dangoosh</t>
+          <t>Max Vance</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>umrbek.xudayorovich@gmail.com</t>
+          <t>max_vance_uz</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1234567</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2024-11-08T10:02:47.978767Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Umrbek Xudayorovich</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pipcoder</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>324304236</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2024-11-08T09:40:52.003144Z</t>
-        </is>
+        <v>8268646737</v>
       </c>
     </row>
   </sheetData>
